--- a/data/Archetype/archetype_squad.xlsx
+++ b/data/Archetype/archetype_squad.xlsx
@@ -479,7 +479,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>SquadRole</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -511,7 +511,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>定位标签</t>
+          <t>队友定位(枚举)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -532,7 +532,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>main_dps</t>
+          <t>MainDps</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -551,7 +551,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>main_dps</t>
+          <t>MainDps</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -570,7 +570,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>support</t>
+          <t>Support</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -589,7 +589,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ranger_dps</t>
+          <t>RangerDps</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -608,7 +608,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>mage_dps</t>
+          <t>MageDps</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -627,7 +627,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>main_dps</t>
+          <t>MainDps</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -646,7 +646,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ranger_dps</t>
+          <t>RangerDps</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -665,7 +665,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>main_dps</t>
+          <t>MainDps</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -684,7 +684,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>mage_dps</t>
+          <t>MageDps</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -703,7 +703,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>support</t>
+          <t>Support</t>
         </is>
       </c>
       <c r="F13" t="n">
